--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="462">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -549,7 +549,7 @@
     <t>Task.basedOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Resource|http://314e.com/fhir/StructureDefinition/account-314e|http://314e.com/fhir/StructureDefinition/allergyintolerance-314e|http://314e.com/fhir/StructureDefinition/appointment-314e|http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/clinicalimpression-314e|http://314e.com/fhir/StructureDefinition/communicationrequest-314e|http://314e.com/fhir/StructureDefinition/condition-314e|http://314e.com/fhir/StructureDefinition/condition-diagnosis-314e|http://314e.com/fhir/StructureDefinition/condition-problem-healthconcern-314e|http://314e.com/fhir/StructureDefinition/contract-314e|http://314e.com/fhir/StructureDefinition/coverage-314e|http://314e.com/fhir/StructureDefinition/detectedissue-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/devicerequest-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-lab-314e|http://314e.com/fhir/StructureDefinition/diagnosticreport-notereport-314e|http://314e.com/fhir/StructureDefinition/documentreference-314e|http://314e.com/fhir/StructureDefinition/encounter-314e|http://314e.com/fhir/StructureDefinition/endpoint-314e|http://314e.com/fhir/StructureDefinition/episodeofcare-314e|http://314e.com/fhir/StructureDefinition/goal-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/imagingstudy-314e|http://314e.com/fhir/StructureDefinition/immunization-314e|http://314e.com/fhir/StructureDefinition/immunizationevaluation-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/location-314e|http://314e.com/fhir/StructureDefinition/media-314e|http://314e.com/fhir/StructureDefinition/medication-314e|http://314e.com/fhir/StructureDefinition/medicationadministration-314e|http://314e.com/fhir/StructureDefinition/medicationdispense-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/molecularsequence-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/observation-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e|http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/procedure-314e|http://314e.com/fhir/StructureDefinition/questionnaireresponse-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/requestgroup-314e|http://314e.com/fhir/StructureDefinition/schedule-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e|http://314e.com/fhir/StructureDefinition/slot-314e|http://314e.com/fhir/StructureDefinition/specimen-314e|http://314e.com/fhir/StructureDefinition/substance-314e|http://314e.com/fhir/StructureDefinition/task-314e|http://314e.com/fhir/StructureDefinition/visionprescription-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -586,7 +586,7 @@
     <t>Task.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Task|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/task-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -893,10 +893,6 @@
     <t>Task.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource) {http://314e.com/fhir/StructureDefinition/reference-314e}
-</t>
-  </si>
-  <si>
     <t>(QI) What task is acting on</t>
   </si>
   <si>
@@ -919,7 +915,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -944,7 +940,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1043,7 +1039,7 @@
     <t>Task.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1099,7 +1095,7 @@
 Executer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e|http://314e.com/fhir/StructureDefinition/healthcareservice-314e|http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/device-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1124,7 +1120,7 @@
     <t>Task.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/location-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1191,7 +1187,7 @@
     <t>Task.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/coverage-314e|ClaimResponse|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1236,7 +1232,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(Provenance) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1337,7 +1333,7 @@
     <t>Task.restriction.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|Organization|4.0.1) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e|http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/relatedperson-314e|http://314e.com/fhir/StructureDefinition/group-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -5142,19 +5138,19 @@
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5221,7 +5217,7 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>240</v>
@@ -5232,14 +5228,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5258,17 +5254,17 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5317,7 +5313,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5332,13 +5328,13 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AM31" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5346,10 +5342,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5372,17 +5368,17 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5431,7 +5427,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5446,13 +5442,13 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AM32" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>20</v>
@@ -5460,10 +5456,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5486,13 +5482,13 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5543,7 +5539,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5558,13 +5554,13 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>311</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5572,14 +5568,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5598,17 +5594,17 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5657,7 +5653,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5666,19 +5662,19 @@
         <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>321</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5686,14 +5682,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5712,17 +5708,17 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5771,7 +5767,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5780,7 +5776,7 @@
         <v>86</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>98</v>
@@ -5789,7 +5785,7 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
@@ -5800,10 +5796,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5826,17 +5822,17 @@
         <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5885,7 +5881,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5900,13 +5896,13 @@
         <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="AL36" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AL36" t="s" s="2">
+      <c r="AM36" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5914,10 +5910,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5943,14 +5939,14 @@
         <v>199</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5978,11 +5974,11 @@
         <v>110</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5999,7 +5995,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6014,13 +6010,13 @@
         <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6028,14 +6024,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6054,19 +6050,19 @@
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6115,7 +6111,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6130,13 +6126,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AL38" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AM38" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6144,10 +6140,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6170,17 +6166,17 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6229,7 +6225,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6244,13 +6240,13 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6258,10 +6254,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6287,13 +6283,13 @@
         <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6322,7 +6318,7 @@
         <v>203</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>20</v>
@@ -6343,7 +6339,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6358,24 +6354,24 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6401,13 +6397,13 @@
         <v>170</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="M41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>372</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>373</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6457,7 +6453,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6472,13 +6468,13 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AL41" t="s" s="2">
-        <v>375</v>
-      </c>
       <c r="AM41" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6486,10 +6482,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6512,13 +6508,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6569,7 +6565,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6584,24 +6580,24 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6624,13 +6620,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6681,7 +6677,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6696,10 +6692,10 @@
         <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>20</v>
@@ -6710,14 +6706,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6736,16 +6732,16 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6795,7 +6791,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6810,10 +6806,10 @@
         <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
@@ -6824,10 +6820,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6850,17 +6846,17 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6909,7 +6905,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6927,7 +6923,7 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
@@ -6938,10 +6934,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7050,10 +7046,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7164,14 +7160,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7193,10 +7189,10 @@
         <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>148</v>
@@ -7251,7 +7247,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7280,10 +7276,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7306,17 +7302,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7365,7 +7361,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7383,7 +7379,7 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
@@ -7394,10 +7390,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7420,19 +7416,19 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7481,7 +7477,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7499,7 +7495,7 @@
         <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>20</v>
@@ -7510,10 +7506,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7536,13 +7532,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7593,7 +7589,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7611,7 +7607,7 @@
         <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>20</v>
@@ -7622,14 +7618,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7648,17 +7644,17 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7707,7 +7703,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7725,7 +7721,7 @@
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7736,10 +7732,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7848,10 +7844,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7962,14 +7958,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7991,10 +7987,10 @@
         <v>131</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>148</v>
@@ -8049,7 +8045,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8078,14 +8074,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8107,16 +8103,16 @@
         <v>199</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>439</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8144,7 +8140,7 @@
         <v>203</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Z56" t="s" s="2">
         <v>20</v>
@@ -8165,7 +8161,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>86</v>
@@ -8183,7 +8179,7 @@
         <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>20</v>
@@ -8194,10 +8190,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8220,13 +8216,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8277,7 +8273,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>86</v>
@@ -8295,7 +8291,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8306,10 +8302,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8332,17 +8328,17 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8391,7 +8387,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8409,7 +8405,7 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
@@ -8420,10 +8416,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8532,10 +8528,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8646,14 +8642,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -8675,10 +8671,10 @@
         <v>131</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>148</v>
@@ -8733,7 +8729,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8762,14 +8758,14 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8791,14 +8787,14 @@
         <v>199</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8826,7 +8822,7 @@
         <v>203</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>20</v>
@@ -8847,7 +8843,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>86</v>
@@ -8865,7 +8861,7 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
@@ -8876,10 +8872,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8902,17 +8898,17 @@
         <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -8961,7 +8957,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>86</v>
@@ -8979,7 +8975,7 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>

--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-task-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-task-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
